--- a/verify-reports/verify-live-report.xlsx
+++ b/verify-reports/verify-live-report.xlsx
@@ -3258,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="G2" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>28</v>
@@ -3284,7 +3284,7 @@
         <v>27</v>
       </c>
       <c r="G3" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3" s="14" t="s">
         <v>28</v>
@@ -3310,7 +3310,7 @@
         <v>27</v>
       </c>
       <c r="G4" s="14">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="H4" s="14" t="s">
         <v>28</v>
@@ -3336,7 +3336,7 @@
         <v>27</v>
       </c>
       <c r="G5" s="14">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H5" s="14" t="s">
         <v>28</v>
@@ -3362,7 +3362,7 @@
         <v>27</v>
       </c>
       <c r="G6" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H6" s="14" t="s">
         <v>28</v>
@@ -3388,7 +3388,7 @@
         <v>27</v>
       </c>
       <c r="G7" s="14">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H7" s="14" t="s">
         <v>28</v>
@@ -3414,7 +3414,7 @@
         <v>27</v>
       </c>
       <c r="G8" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H8" s="14" t="s">
         <v>28</v>
@@ -3440,7 +3440,7 @@
         <v>27</v>
       </c>
       <c r="G9" s="14">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>28</v>
@@ -3466,7 +3466,7 @@
         <v>27</v>
       </c>
       <c r="G10" s="14">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H10" s="14" t="s">
         <v>28</v>
@@ -3492,7 +3492,7 @@
         <v>27</v>
       </c>
       <c r="G11" s="14">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H11" s="14" t="s">
         <v>28</v>
@@ -3518,7 +3518,7 @@
         <v>27</v>
       </c>
       <c r="G12" s="14">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H12" s="14" t="s">
         <v>28</v>
@@ -3544,7 +3544,7 @@
         <v>27</v>
       </c>
       <c r="G13" s="14">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="H13" s="14" t="s">
         <v>28</v>
@@ -3570,7 +3570,7 @@
         <v>27</v>
       </c>
       <c r="G14" s="14">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H14" s="14" t="s">
         <v>28</v>
@@ -3596,7 +3596,7 @@
         <v>27</v>
       </c>
       <c r="G15" s="14">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H15" s="14" t="s">
         <v>28</v>
@@ -3622,7 +3622,7 @@
         <v>27</v>
       </c>
       <c r="G16" s="14">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H16" s="14" t="s">
         <v>28</v>
@@ -3648,7 +3648,7 @@
         <v>27</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H17" s="14" t="s">
         <v>28</v>
@@ -3674,7 +3674,7 @@
         <v>27</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H18" s="14" t="s">
         <v>28</v>
@@ -3700,7 +3700,7 @@
         <v>27</v>
       </c>
       <c r="G19" s="14">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="H19" s="14" t="s">
         <v>28</v>
@@ -3726,7 +3726,7 @@
         <v>27</v>
       </c>
       <c r="G20" s="14">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14" t="s">
         <v>28</v>
@@ -3752,7 +3752,7 @@
         <v>27</v>
       </c>
       <c r="G21" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H21" s="14" t="s">
         <v>28</v>
@@ -3804,7 +3804,7 @@
         <v>27</v>
       </c>
       <c r="G23" s="14">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H23" s="14" t="s">
         <v>28</v>
@@ -3830,7 +3830,7 @@
         <v>27</v>
       </c>
       <c r="G24" s="14">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H24" s="14" t="s">
         <v>28</v>
@@ -3856,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="G25" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H25" s="14" t="s">
         <v>28</v>
@@ -3882,7 +3882,7 @@
         <v>27</v>
       </c>
       <c r="G26" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H26" s="14" t="s">
         <v>28</v>
@@ -3908,7 +3908,7 @@
         <v>27</v>
       </c>
       <c r="G27" s="14">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H27" s="14" t="s">
         <v>28</v>
@@ -3934,7 +3934,7 @@
         <v>27</v>
       </c>
       <c r="G28" s="14">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H28" s="14" t="s">
         <v>28</v>
@@ -3960,7 +3960,7 @@
         <v>27</v>
       </c>
       <c r="G29" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H29" s="14" t="s">
         <v>28</v>
@@ -3986,7 +3986,7 @@
         <v>27</v>
       </c>
       <c r="G30" s="14">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H30" s="14" t="s">
         <v>28</v>
@@ -4012,7 +4012,7 @@
         <v>27</v>
       </c>
       <c r="G31" s="14">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="H31" s="14" t="s">
         <v>28</v>
@@ -4038,7 +4038,7 @@
         <v>27</v>
       </c>
       <c r="G32" s="14">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H32" s="14" t="s">
         <v>28</v>
@@ -4064,7 +4064,7 @@
         <v>27</v>
       </c>
       <c r="G33" s="14">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H33" s="14" t="s">
         <v>28</v>
@@ -4090,7 +4090,7 @@
         <v>27</v>
       </c>
       <c r="G34" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H34" s="14" t="s">
         <v>28</v>
@@ -4116,7 +4116,7 @@
         <v>27</v>
       </c>
       <c r="G35" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H35" s="14" t="s">
         <v>28</v>
@@ -4142,7 +4142,7 @@
         <v>27</v>
       </c>
       <c r="G36" s="14">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H36" s="14" t="s">
         <v>28</v>
@@ -4168,7 +4168,7 @@
         <v>27</v>
       </c>
       <c r="G37" s="14">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H37" s="14" t="s">
         <v>28</v>
@@ -4194,7 +4194,7 @@
         <v>27</v>
       </c>
       <c r="G38" s="14">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H38" s="14" t="s">
         <v>28</v>
@@ -4220,7 +4220,7 @@
         <v>27</v>
       </c>
       <c r="G39" s="14">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H39" s="14" t="s">
         <v>28</v>
@@ -4246,7 +4246,7 @@
         <v>27</v>
       </c>
       <c r="G40" s="14">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H40" s="14" t="s">
         <v>28</v>
@@ -4272,7 +4272,7 @@
         <v>27</v>
       </c>
       <c r="G41" s="14">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H41" s="14" t="s">
         <v>28</v>
@@ -4298,7 +4298,7 @@
         <v>27</v>
       </c>
       <c r="G42" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H42" s="14" t="s">
         <v>28</v>
@@ -4324,7 +4324,7 @@
         <v>27</v>
       </c>
       <c r="G43" s="14">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H43" s="14" t="s">
         <v>28</v>
@@ -4350,7 +4350,7 @@
         <v>27</v>
       </c>
       <c r="G44" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H44" s="14" t="s">
         <v>28</v>
@@ -4376,7 +4376,7 @@
         <v>27</v>
       </c>
       <c r="G45" s="14">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H45" s="14" t="s">
         <v>28</v>
@@ -4402,7 +4402,7 @@
         <v>27</v>
       </c>
       <c r="G46" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H46" s="14" t="s">
         <v>28</v>
@@ -4428,7 +4428,7 @@
         <v>27</v>
       </c>
       <c r="G47" s="14">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H47" s="14" t="s">
         <v>28</v>
@@ -4454,7 +4454,7 @@
         <v>27</v>
       </c>
       <c r="G48" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H48" s="14" t="s">
         <v>28</v>
@@ -4480,7 +4480,7 @@
         <v>27</v>
       </c>
       <c r="G49" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H49" s="14" t="s">
         <v>28</v>
@@ -4506,7 +4506,7 @@
         <v>27</v>
       </c>
       <c r="G50" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H50" s="14" t="s">
         <v>28</v>
@@ -4532,7 +4532,7 @@
         <v>27</v>
       </c>
       <c r="G51" s="14">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H51" s="14" t="s">
         <v>28</v>
@@ -4558,7 +4558,7 @@
         <v>27</v>
       </c>
       <c r="G52" s="14">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H52" s="14" t="s">
         <v>28</v>
@@ -4584,7 +4584,7 @@
         <v>27</v>
       </c>
       <c r="G53" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H53" s="14" t="s">
         <v>28</v>
@@ -4610,7 +4610,7 @@
         <v>27</v>
       </c>
       <c r="G54" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H54" s="14" t="s">
         <v>28</v>
@@ -4636,7 +4636,7 @@
         <v>27</v>
       </c>
       <c r="G55" s="14">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H55" s="14" t="s">
         <v>28</v>
@@ -4662,7 +4662,7 @@
         <v>27</v>
       </c>
       <c r="G56" s="14">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H56" s="14" t="s">
         <v>28</v>
@@ -4688,7 +4688,7 @@
         <v>27</v>
       </c>
       <c r="G57" s="14">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H57" s="14" t="s">
         <v>28</v>
@@ -4714,7 +4714,7 @@
         <v>27</v>
       </c>
       <c r="G58" s="14">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H58" s="14" t="s">
         <v>28</v>
@@ -4740,7 +4740,7 @@
         <v>27</v>
       </c>
       <c r="G59" s="14">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H59" s="14" t="s">
         <v>28</v>
@@ -4766,7 +4766,7 @@
         <v>27</v>
       </c>
       <c r="G60" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H60" s="14" t="s">
         <v>28</v>
@@ -4792,7 +4792,7 @@
         <v>27</v>
       </c>
       <c r="G61" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H61" s="14" t="s">
         <v>28</v>
@@ -4818,7 +4818,7 @@
         <v>27</v>
       </c>
       <c r="G62" s="14">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H62" s="14" t="s">
         <v>28</v>
@@ -4844,7 +4844,7 @@
         <v>27</v>
       </c>
       <c r="G63" s="14">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H63" s="14" t="s">
         <v>28</v>
@@ -4870,7 +4870,7 @@
         <v>27</v>
       </c>
       <c r="G64" s="14">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="H64" s="14" t="s">
         <v>28</v>
@@ -4896,7 +4896,7 @@
         <v>27</v>
       </c>
       <c r="G65" s="14">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H65" s="14" t="s">
         <v>28</v>
@@ -4922,7 +4922,7 @@
         <v>27</v>
       </c>
       <c r="G66" s="14">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H66" s="14" t="s">
         <v>28</v>
@@ -4948,7 +4948,7 @@
         <v>27</v>
       </c>
       <c r="G67" s="14">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H67" s="14" t="s">
         <v>28</v>
@@ -4974,7 +4974,7 @@
         <v>27</v>
       </c>
       <c r="G68" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H68" s="14" t="s">
         <v>28</v>
@@ -5000,7 +5000,7 @@
         <v>27</v>
       </c>
       <c r="G69" s="14">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H69" s="14" t="s">
         <v>28</v>
@@ -5026,7 +5026,7 @@
         <v>27</v>
       </c>
       <c r="G70" s="14">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H70" s="14" t="s">
         <v>28</v>
@@ -5052,7 +5052,7 @@
         <v>27</v>
       </c>
       <c r="G71" s="14">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H71" s="14" t="s">
         <v>28</v>
@@ -5078,7 +5078,7 @@
         <v>27</v>
       </c>
       <c r="G72" s="14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H72" s="14" t="s">
         <v>28</v>
@@ -5104,7 +5104,7 @@
         <v>27</v>
       </c>
       <c r="G73" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H73" s="14" t="s">
         <v>28</v>
@@ -5130,7 +5130,7 @@
         <v>27</v>
       </c>
       <c r="G74" s="14">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="H74" s="14" t="s">
         <v>28</v>
@@ -5156,7 +5156,7 @@
         <v>27</v>
       </c>
       <c r="G75" s="14">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H75" s="14" t="s">
         <v>28</v>
@@ -5182,7 +5182,7 @@
         <v>27</v>
       </c>
       <c r="G76" s="14">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H76" s="14" t="s">
         <v>28</v>
@@ -5208,7 +5208,7 @@
         <v>27</v>
       </c>
       <c r="G77" s="14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H77" s="14" t="s">
         <v>28</v>
@@ -5234,7 +5234,7 @@
         <v>27</v>
       </c>
       <c r="G78" s="14">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H78" s="14" t="s">
         <v>28</v>
@@ -5260,7 +5260,7 @@
         <v>27</v>
       </c>
       <c r="G79" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H79" s="14" t="s">
         <v>28</v>
@@ -5286,7 +5286,7 @@
         <v>27</v>
       </c>
       <c r="G80" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H80" s="14" t="s">
         <v>28</v>
@@ -5312,7 +5312,7 @@
         <v>27</v>
       </c>
       <c r="G81" s="14">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H81" s="14" t="s">
         <v>28</v>
@@ -5338,7 +5338,7 @@
         <v>27</v>
       </c>
       <c r="G82" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H82" s="14" t="s">
         <v>28</v>
@@ -5364,7 +5364,7 @@
         <v>27</v>
       </c>
       <c r="G83" s="14">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H83" s="14" t="s">
         <v>28</v>
@@ -5390,7 +5390,7 @@
         <v>27</v>
       </c>
       <c r="G84" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H84" s="14" t="s">
         <v>28</v>
@@ -5416,7 +5416,7 @@
         <v>27</v>
       </c>
       <c r="G85" s="14">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H85" s="14" t="s">
         <v>28</v>
@@ -5442,7 +5442,7 @@
         <v>27</v>
       </c>
       <c r="G86" s="14">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H86" s="14" t="s">
         <v>28</v>
@@ -5468,7 +5468,7 @@
         <v>27</v>
       </c>
       <c r="G87" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H87" s="14" t="s">
         <v>28</v>
@@ -5494,7 +5494,7 @@
         <v>27</v>
       </c>
       <c r="G88" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H88" s="14" t="s">
         <v>28</v>
@@ -5520,7 +5520,7 @@
         <v>27</v>
       </c>
       <c r="G89" s="14">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H89" s="14" t="s">
         <v>28</v>
@@ -5546,7 +5546,7 @@
         <v>27</v>
       </c>
       <c r="G90" s="14">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H90" s="14" t="s">
         <v>28</v>
@@ -5572,7 +5572,7 @@
         <v>27</v>
       </c>
       <c r="G91" s="14">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H91" s="14" t="s">
         <v>28</v>
@@ -5598,7 +5598,7 @@
         <v>27</v>
       </c>
       <c r="G92" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H92" s="14" t="s">
         <v>28</v>
@@ -5624,7 +5624,7 @@
         <v>27</v>
       </c>
       <c r="G93" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H93" s="14" t="s">
         <v>28</v>
@@ -5650,7 +5650,7 @@
         <v>27</v>
       </c>
       <c r="G94" s="14">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="H94" s="14" t="s">
         <v>28</v>
@@ -5676,7 +5676,7 @@
         <v>27</v>
       </c>
       <c r="G95" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H95" s="14" t="s">
         <v>28</v>
@@ -5702,7 +5702,7 @@
         <v>27</v>
       </c>
       <c r="G96" s="14">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="H96" s="14" t="s">
         <v>28</v>
@@ -5728,7 +5728,7 @@
         <v>27</v>
       </c>
       <c r="G97" s="14">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="H97" s="14" t="s">
         <v>28</v>
@@ -5754,7 +5754,7 @@
         <v>27</v>
       </c>
       <c r="G98" s="14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H98" s="14" t="s">
         <v>28</v>
@@ -5780,7 +5780,7 @@
         <v>27</v>
       </c>
       <c r="G99" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H99" s="14" t="s">
         <v>28</v>
@@ -5806,7 +5806,7 @@
         <v>27</v>
       </c>
       <c r="G100" s="14">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H100" s="14" t="s">
         <v>28</v>
@@ -5832,7 +5832,7 @@
         <v>27</v>
       </c>
       <c r="G101" s="14">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="H101" s="14" t="s">
         <v>28</v>
@@ -5858,7 +5858,7 @@
         <v>27</v>
       </c>
       <c r="G102" s="14">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H102" s="14" t="s">
         <v>28</v>
@@ -5884,7 +5884,7 @@
         <v>27</v>
       </c>
       <c r="G103" s="14">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H103" s="14" t="s">
         <v>28</v>
@@ -5910,7 +5910,7 @@
         <v>27</v>
       </c>
       <c r="G104" s="14">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="H104" s="14" t="s">
         <v>28</v>
@@ -5936,7 +5936,7 @@
         <v>27</v>
       </c>
       <c r="G105" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H105" s="14" t="s">
         <v>28</v>
@@ -5962,7 +5962,7 @@
         <v>27</v>
       </c>
       <c r="G106" s="14">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H106" s="14" t="s">
         <v>28</v>
@@ -5988,7 +5988,7 @@
         <v>27</v>
       </c>
       <c r="G107" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H107" s="14" t="s">
         <v>28</v>
@@ -6014,7 +6014,7 @@
         <v>27</v>
       </c>
       <c r="G108" s="14">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="H108" s="14" t="s">
         <v>28</v>
@@ -6040,7 +6040,7 @@
         <v>27</v>
       </c>
       <c r="G109" s="14">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H109" s="14" t="s">
         <v>28</v>
@@ -6066,7 +6066,7 @@
         <v>27</v>
       </c>
       <c r="G110" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H110" s="14" t="s">
         <v>28</v>
@@ -6092,7 +6092,7 @@
         <v>27</v>
       </c>
       <c r="G111" s="14">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H111" s="14" t="s">
         <v>28</v>
@@ -6118,7 +6118,7 @@
         <v>27</v>
       </c>
       <c r="G112" s="14">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H112" s="14" t="s">
         <v>28</v>
@@ -6144,7 +6144,7 @@
         <v>27</v>
       </c>
       <c r="G113" s="14">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H113" s="14" t="s">
         <v>28</v>
@@ -6170,7 +6170,7 @@
         <v>27</v>
       </c>
       <c r="G114" s="14">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H114" s="14" t="s">
         <v>28</v>
@@ -6196,7 +6196,7 @@
         <v>27</v>
       </c>
       <c r="G115" s="14">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="H115" s="14" t="s">
         <v>28</v>
@@ -6222,7 +6222,7 @@
         <v>27</v>
       </c>
       <c r="G116" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H116" s="14" t="s">
         <v>28</v>
@@ -6248,7 +6248,7 @@
         <v>27</v>
       </c>
       <c r="G117" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H117" s="14" t="s">
         <v>28</v>
@@ -6274,7 +6274,7 @@
         <v>27</v>
       </c>
       <c r="G118" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H118" s="14" t="s">
         <v>28</v>
@@ -6300,7 +6300,7 @@
         <v>27</v>
       </c>
       <c r="G119" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H119" s="14" t="s">
         <v>28</v>
@@ -6326,7 +6326,7 @@
         <v>27</v>
       </c>
       <c r="G120" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H120" s="14" t="s">
         <v>28</v>
@@ -6378,7 +6378,7 @@
         <v>27</v>
       </c>
       <c r="G122" s="14">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H122" s="14" t="s">
         <v>28</v>
@@ -6404,7 +6404,7 @@
         <v>27</v>
       </c>
       <c r="G123" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H123" s="14" t="s">
         <v>28</v>
@@ -6430,7 +6430,7 @@
         <v>27</v>
       </c>
       <c r="G124" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H124" s="14" t="s">
         <v>28</v>
@@ -6456,7 +6456,7 @@
         <v>27</v>
       </c>
       <c r="G125" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H125" s="14" t="s">
         <v>28</v>
@@ -6482,7 +6482,7 @@
         <v>27</v>
       </c>
       <c r="G126" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H126" s="14" t="s">
         <v>28</v>
@@ -6508,7 +6508,7 @@
         <v>27</v>
       </c>
       <c r="G127" s="14">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H127" s="14" t="s">
         <v>28</v>
@@ -6534,7 +6534,7 @@
         <v>27</v>
       </c>
       <c r="G128" s="14">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="H128" s="14" t="s">
         <v>28</v>
@@ -6560,7 +6560,7 @@
         <v>27</v>
       </c>
       <c r="G129" s="14">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H129" s="14" t="s">
         <v>28</v>
@@ -6586,7 +6586,7 @@
         <v>27</v>
       </c>
       <c r="G130" s="14">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="H130" s="14" t="s">
         <v>28</v>
@@ -6612,7 +6612,7 @@
         <v>27</v>
       </c>
       <c r="G131" s="14">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H131" s="14" t="s">
         <v>28</v>
@@ -6638,7 +6638,7 @@
         <v>27</v>
       </c>
       <c r="G132" s="14">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H132" s="14" t="s">
         <v>28</v>
@@ -6664,7 +6664,7 @@
         <v>27</v>
       </c>
       <c r="G133" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H133" s="14" t="s">
         <v>28</v>
@@ -6716,7 +6716,7 @@
         <v>27</v>
       </c>
       <c r="G135" s="14">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H135" s="14" t="s">
         <v>28</v>
@@ -6742,7 +6742,7 @@
         <v>27</v>
       </c>
       <c r="G136" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H136" s="14" t="s">
         <v>28</v>
@@ -6768,7 +6768,7 @@
         <v>27</v>
       </c>
       <c r="G137" s="14">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H137" s="14" t="s">
         <v>28</v>
@@ -6794,7 +6794,7 @@
         <v>27</v>
       </c>
       <c r="G138" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H138" s="14" t="s">
         <v>28</v>
@@ -6820,7 +6820,7 @@
         <v>27</v>
       </c>
       <c r="G139" s="14">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H139" s="14" t="s">
         <v>28</v>
@@ -6846,7 +6846,7 @@
         <v>27</v>
       </c>
       <c r="G140" s="14">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H140" s="14" t="s">
         <v>28</v>
@@ -6872,7 +6872,7 @@
         <v>27</v>
       </c>
       <c r="G141" s="14">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="H141" s="14" t="s">
         <v>28</v>
@@ -6898,7 +6898,7 @@
         <v>27</v>
       </c>
       <c r="G142" s="14">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H142" s="14" t="s">
         <v>28</v>
@@ -6924,7 +6924,7 @@
         <v>27</v>
       </c>
       <c r="G143" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H143" s="14" t="s">
         <v>28</v>
@@ -6950,7 +6950,7 @@
         <v>27</v>
       </c>
       <c r="G144" s="14">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H144" s="14" t="s">
         <v>28</v>
@@ -6976,7 +6976,7 @@
         <v>27</v>
       </c>
       <c r="G145" s="14">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H145" s="14" t="s">
         <v>28</v>
@@ -7002,7 +7002,7 @@
         <v>27</v>
       </c>
       <c r="G146" s="14">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H146" s="14" t="s">
         <v>28</v>
@@ -7028,7 +7028,7 @@
         <v>27</v>
       </c>
       <c r="G147" s="14">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H147" s="14" t="s">
         <v>28</v>
@@ -7054,7 +7054,7 @@
         <v>27</v>
       </c>
       <c r="G148" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H148" s="14" t="s">
         <v>28</v>
@@ -7080,7 +7080,7 @@
         <v>27</v>
       </c>
       <c r="G149" s="14">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H149" s="14" t="s">
         <v>28</v>
@@ -7106,7 +7106,7 @@
         <v>27</v>
       </c>
       <c r="G150" s="14">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="H150" s="14" t="s">
         <v>28</v>
@@ -7132,7 +7132,7 @@
         <v>27</v>
       </c>
       <c r="G151" s="14">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H151" s="14" t="s">
         <v>28</v>
@@ -7158,7 +7158,7 @@
         <v>27</v>
       </c>
       <c r="G152" s="14">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H152" s="14" t="s">
         <v>28</v>
@@ -7184,7 +7184,7 @@
         <v>27</v>
       </c>
       <c r="G153" s="14">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="H153" s="14" t="s">
         <v>28</v>
@@ -7210,7 +7210,7 @@
         <v>27</v>
       </c>
       <c r="G154" s="14">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H154" s="14" t="s">
         <v>28</v>
@@ -7236,7 +7236,7 @@
         <v>27</v>
       </c>
       <c r="G155" s="14">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="H155" s="14" t="s">
         <v>28</v>
@@ -7288,7 +7288,7 @@
         <v>27</v>
       </c>
       <c r="G157" s="14">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H157" s="14" t="s">
         <v>28</v>
@@ -7314,7 +7314,7 @@
         <v>27</v>
       </c>
       <c r="G158" s="14">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="H158" s="14" t="s">
         <v>28</v>
@@ -7340,7 +7340,7 @@
         <v>27</v>
       </c>
       <c r="G159" s="14">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H159" s="14" t="s">
         <v>28</v>
@@ -7366,7 +7366,7 @@
         <v>27</v>
       </c>
       <c r="G160" s="14">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H160" s="14" t="s">
         <v>28</v>
@@ -7392,7 +7392,7 @@
         <v>27</v>
       </c>
       <c r="G161" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H161" s="14" t="s">
         <v>28</v>
@@ -7418,7 +7418,7 @@
         <v>27</v>
       </c>
       <c r="G162" s="14">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H162" s="14" t="s">
         <v>28</v>
@@ -7444,7 +7444,7 @@
         <v>27</v>
       </c>
       <c r="G163" s="14">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H163" s="14" t="s">
         <v>28</v>
@@ -7470,7 +7470,7 @@
         <v>27</v>
       </c>
       <c r="G164" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="H164" s="14" t="s">
         <v>28</v>
@@ -7496,7 +7496,7 @@
         <v>27</v>
       </c>
       <c r="G165" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H165" s="14" t="s">
         <v>28</v>
@@ -7522,7 +7522,7 @@
         <v>27</v>
       </c>
       <c r="G166" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H166" s="14" t="s">
         <v>28</v>
@@ -7548,7 +7548,7 @@
         <v>27</v>
       </c>
       <c r="G167" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H167" s="14" t="s">
         <v>28</v>
@@ -7574,7 +7574,7 @@
         <v>27</v>
       </c>
       <c r="G168" s="14">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="H168" s="14" t="s">
         <v>28</v>
@@ -7600,7 +7600,7 @@
         <v>27</v>
       </c>
       <c r="G169" s="14">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H169" s="14" t="s">
         <v>28</v>
@@ -7626,7 +7626,7 @@
         <v>27</v>
       </c>
       <c r="G170" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H170" s="14" t="s">
         <v>28</v>
@@ -7678,7 +7678,7 @@
         <v>27</v>
       </c>
       <c r="G172" s="14">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="H172" s="14" t="s">
         <v>28</v>
@@ -7704,7 +7704,7 @@
         <v>27</v>
       </c>
       <c r="G173" s="14">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H173" s="14" t="s">
         <v>28</v>
@@ -7730,7 +7730,7 @@
         <v>27</v>
       </c>
       <c r="G174" s="14">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H174" s="14" t="s">
         <v>28</v>
@@ -7756,7 +7756,7 @@
         <v>27</v>
       </c>
       <c r="G175" s="14">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="H175" s="14" t="s">
         <v>28</v>
@@ -7782,7 +7782,7 @@
         <v>27</v>
       </c>
       <c r="G176" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H176" s="14" t="s">
         <v>28</v>
@@ -7808,7 +7808,7 @@
         <v>27</v>
       </c>
       <c r="G177" s="14">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="H177" s="14" t="s">
         <v>28</v>
@@ -7834,7 +7834,7 @@
         <v>27</v>
       </c>
       <c r="G178" s="14">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H178" s="14" t="s">
         <v>28</v>
@@ -7860,7 +7860,7 @@
         <v>27</v>
       </c>
       <c r="G179" s="14">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H179" s="14" t="s">
         <v>28</v>
@@ -7886,7 +7886,7 @@
         <v>27</v>
       </c>
       <c r="G180" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H180" s="14" t="s">
         <v>28</v>
@@ -7912,7 +7912,7 @@
         <v>27</v>
       </c>
       <c r="G181" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H181" s="14" t="s">
         <v>28</v>
@@ -7938,7 +7938,7 @@
         <v>27</v>
       </c>
       <c r="G182" s="14">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H182" s="14" t="s">
         <v>28</v>
@@ -7964,7 +7964,7 @@
         <v>27</v>
       </c>
       <c r="G183" s="14">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H183" s="14" t="s">
         <v>28</v>
@@ -7990,7 +7990,7 @@
         <v>27</v>
       </c>
       <c r="G184" s="14">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H184" s="14" t="s">
         <v>28</v>
@@ -8016,7 +8016,7 @@
         <v>27</v>
       </c>
       <c r="G185" s="14">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="H185" s="14" t="s">
         <v>28</v>
@@ -8042,7 +8042,7 @@
         <v>27</v>
       </c>
       <c r="G186" s="14">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H186" s="14" t="s">
         <v>28</v>
@@ -8068,7 +8068,7 @@
         <v>27</v>
       </c>
       <c r="G187" s="14">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="H187" s="14" t="s">
         <v>28</v>
@@ -8094,7 +8094,7 @@
         <v>27</v>
       </c>
       <c r="G188" s="14">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H188" s="14" t="s">
         <v>28</v>
@@ -8120,7 +8120,7 @@
         <v>27</v>
       </c>
       <c r="G189" s="14">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H189" s="14" t="s">
         <v>28</v>
@@ -8146,7 +8146,7 @@
         <v>27</v>
       </c>
       <c r="G190" s="14">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="H190" s="14" t="s">
         <v>28</v>
@@ -8172,7 +8172,7 @@
         <v>27</v>
       </c>
       <c r="G191" s="14">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H191" s="14" t="s">
         <v>28</v>
@@ -8198,7 +8198,7 @@
         <v>27</v>
       </c>
       <c r="G192" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H192" s="14" t="s">
         <v>28</v>
@@ -8224,7 +8224,7 @@
         <v>27</v>
       </c>
       <c r="G193" s="14">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H193" s="14" t="s">
         <v>28</v>
@@ -8250,7 +8250,7 @@
         <v>27</v>
       </c>
       <c r="G194" s="14">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H194" s="14" t="s">
         <v>28</v>
@@ -8302,7 +8302,7 @@
         <v>27</v>
       </c>
       <c r="G196" s="14">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H196" s="14" t="s">
         <v>28</v>
@@ -8328,7 +8328,7 @@
         <v>27</v>
       </c>
       <c r="G197" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H197" s="14" t="s">
         <v>28</v>
@@ -8354,7 +8354,7 @@
         <v>27</v>
       </c>
       <c r="G198" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H198" s="14" t="s">
         <v>28</v>
@@ -8380,7 +8380,7 @@
         <v>27</v>
       </c>
       <c r="G199" s="14">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H199" s="14" t="s">
         <v>28</v>
@@ -8406,7 +8406,7 @@
         <v>27</v>
       </c>
       <c r="G200" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H200" s="14" t="s">
         <v>28</v>
@@ -8432,7 +8432,7 @@
         <v>27</v>
       </c>
       <c r="G201" s="14">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H201" s="14" t="s">
         <v>28</v>
@@ -8458,7 +8458,7 @@
         <v>27</v>
       </c>
       <c r="G202" s="14">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H202" s="14" t="s">
         <v>28</v>
@@ -8484,7 +8484,7 @@
         <v>27</v>
       </c>
       <c r="G203" s="14">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H203" s="14" t="s">
         <v>28</v>
@@ -8510,7 +8510,7 @@
         <v>27</v>
       </c>
       <c r="G204" s="14">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="H204" s="14" t="s">
         <v>28</v>
@@ -8536,7 +8536,7 @@
         <v>27</v>
       </c>
       <c r="G205" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H205" s="14" t="s">
         <v>28</v>
@@ -8562,7 +8562,7 @@
         <v>27</v>
       </c>
       <c r="G206" s="14">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="H206" s="14" t="s">
         <v>28</v>
@@ -8588,7 +8588,7 @@
         <v>27</v>
       </c>
       <c r="G207" s="14">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="H207" s="14" t="s">
         <v>28</v>
@@ -8614,7 +8614,7 @@
         <v>27</v>
       </c>
       <c r="G208" s="14">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H208" s="14" t="s">
         <v>28</v>
@@ -8640,7 +8640,7 @@
         <v>27</v>
       </c>
       <c r="G209" s="14">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H209" s="14" t="s">
         <v>28</v>
@@ -8692,7 +8692,7 @@
         <v>27</v>
       </c>
       <c r="G211" s="14">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H211" s="14" t="s">
         <v>28</v>
@@ -8718,7 +8718,7 @@
         <v>27</v>
       </c>
       <c r="G212" s="14">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H212" s="14" t="s">
         <v>28</v>
@@ -8744,7 +8744,7 @@
         <v>27</v>
       </c>
       <c r="G213" s="14">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H213" s="14" t="s">
         <v>28</v>
@@ -8770,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="G214" s="14">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H214" s="14" t="s">
         <v>28</v>
@@ -8796,7 +8796,7 @@
         <v>27</v>
       </c>
       <c r="G215" s="14">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H215" s="14" t="s">
         <v>28</v>
@@ -8822,7 +8822,7 @@
         <v>27</v>
       </c>
       <c r="G216" s="14">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H216" s="14" t="s">
         <v>28</v>
@@ -8848,7 +8848,7 @@
         <v>27</v>
       </c>
       <c r="G217" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H217" s="14" t="s">
         <v>28</v>
@@ -8874,7 +8874,7 @@
         <v>27</v>
       </c>
       <c r="G218" s="14">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H218" s="14" t="s">
         <v>28</v>
@@ -8900,7 +8900,7 @@
         <v>27</v>
       </c>
       <c r="G219" s="14">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H219" s="14" t="s">
         <v>28</v>
@@ -8926,7 +8926,7 @@
         <v>27</v>
       </c>
       <c r="G220" s="14">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H220" s="14" t="s">
         <v>28</v>
@@ -8952,7 +8952,7 @@
         <v>27</v>
       </c>
       <c r="G221" s="14">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H221" s="14" t="s">
         <v>28</v>
@@ -8978,7 +8978,7 @@
         <v>27</v>
       </c>
       <c r="G222" s="14">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H222" s="14" t="s">
         <v>28</v>
@@ -9004,7 +9004,7 @@
         <v>27</v>
       </c>
       <c r="G223" s="14">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="H223" s="14" t="s">
         <v>28</v>
@@ -9030,7 +9030,7 @@
         <v>27</v>
       </c>
       <c r="G224" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H224" s="14" t="s">
         <v>28</v>
@@ -9056,7 +9056,7 @@
         <v>27</v>
       </c>
       <c r="G225" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H225" s="14" t="s">
         <v>28</v>
@@ -9082,7 +9082,7 @@
         <v>27</v>
       </c>
       <c r="G226" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H226" s="14" t="s">
         <v>28</v>
@@ -9108,7 +9108,7 @@
         <v>27</v>
       </c>
       <c r="G227" s="14">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H227" s="14" t="s">
         <v>28</v>
@@ -9134,7 +9134,7 @@
         <v>27</v>
       </c>
       <c r="G228" s="14">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="H228" s="14" t="s">
         <v>28</v>
@@ -9160,7 +9160,7 @@
         <v>27</v>
       </c>
       <c r="G229" s="14">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H229" s="14" t="s">
         <v>28</v>
@@ -9186,7 +9186,7 @@
         <v>27</v>
       </c>
       <c r="G230" s="14">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H230" s="14" t="s">
         <v>28</v>
@@ -9212,7 +9212,7 @@
         <v>27</v>
       </c>
       <c r="G231" s="14">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H231" s="14" t="s">
         <v>28</v>
@@ -9238,7 +9238,7 @@
         <v>27</v>
       </c>
       <c r="G232" s="14">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H232" s="14" t="s">
         <v>28</v>
@@ -9264,7 +9264,7 @@
         <v>27</v>
       </c>
       <c r="G233" s="14">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H233" s="14" t="s">
         <v>28</v>
@@ -9290,7 +9290,7 @@
         <v>27</v>
       </c>
       <c r="G234" s="14">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H234" s="14" t="s">
         <v>28</v>
@@ -9316,7 +9316,7 @@
         <v>27</v>
       </c>
       <c r="G235" s="14">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="H235" s="14" t="s">
         <v>28</v>
@@ -9342,7 +9342,7 @@
         <v>27</v>
       </c>
       <c r="G236" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H236" s="14" t="s">
         <v>28</v>
@@ -9368,7 +9368,7 @@
         <v>27</v>
       </c>
       <c r="G237" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H237" s="14" t="s">
         <v>28</v>
@@ -9394,7 +9394,7 @@
         <v>27</v>
       </c>
       <c r="G238" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H238" s="14" t="s">
         <v>28</v>
@@ -9420,7 +9420,7 @@
         <v>27</v>
       </c>
       <c r="G239" s="14">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H239" s="14" t="s">
         <v>28</v>
@@ -9446,7 +9446,7 @@
         <v>27</v>
       </c>
       <c r="G240" s="14">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="H240" s="14" t="s">
         <v>28</v>
@@ -9472,7 +9472,7 @@
         <v>27</v>
       </c>
       <c r="G241" s="14">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H241" s="14" t="s">
         <v>28</v>
@@ -9498,7 +9498,7 @@
         <v>27</v>
       </c>
       <c r="G242" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H242" s="14" t="s">
         <v>28</v>
@@ -9524,7 +9524,7 @@
         <v>27</v>
       </c>
       <c r="G243" s="14">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H243" s="14" t="s">
         <v>28</v>
@@ -9550,7 +9550,7 @@
         <v>27</v>
       </c>
       <c r="G244" s="14">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H244" s="14" t="s">
         <v>28</v>
@@ -9576,7 +9576,7 @@
         <v>27</v>
       </c>
       <c r="G245" s="14">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H245" s="14" t="s">
         <v>28</v>
@@ -9602,7 +9602,7 @@
         <v>27</v>
       </c>
       <c r="G246" s="14">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H246" s="14" t="s">
         <v>28</v>
@@ -9654,7 +9654,7 @@
         <v>27</v>
       </c>
       <c r="G248" s="14">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H248" s="14" t="s">
         <v>28</v>
@@ -9680,7 +9680,7 @@
         <v>27</v>
       </c>
       <c r="G249" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H249" s="14" t="s">
         <v>28</v>
@@ -9706,7 +9706,7 @@
         <v>27</v>
       </c>
       <c r="G250" s="14">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H250" s="14" t="s">
         <v>28</v>
@@ -9758,7 +9758,7 @@
         <v>27</v>
       </c>
       <c r="G252" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H252" s="14" t="s">
         <v>28</v>
@@ -9784,7 +9784,7 @@
         <v>27</v>
       </c>
       <c r="G253" s="14">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H253" s="14" t="s">
         <v>28</v>
@@ -9810,7 +9810,7 @@
         <v>27</v>
       </c>
       <c r="G254" s="14">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H254" s="14" t="s">
         <v>28</v>
@@ -9836,7 +9836,7 @@
         <v>27</v>
       </c>
       <c r="G255" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H255" s="14" t="s">
         <v>28</v>
@@ -9862,7 +9862,7 @@
         <v>27</v>
       </c>
       <c r="G256" s="14">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H256" s="14" t="s">
         <v>28</v>
@@ -9888,7 +9888,7 @@
         <v>27</v>
       </c>
       <c r="G257" s="14">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="H257" s="14" t="s">
         <v>28</v>
@@ -9914,7 +9914,7 @@
         <v>27</v>
       </c>
       <c r="G258" s="14">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H258" s="14" t="s">
         <v>28</v>
@@ -9940,7 +9940,7 @@
         <v>27</v>
       </c>
       <c r="G259" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H259" s="14" t="s">
         <v>28</v>
@@ -9966,7 +9966,7 @@
         <v>27</v>
       </c>
       <c r="G260" s="14">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H260" s="14" t="s">
         <v>28</v>
@@ -9992,7 +9992,7 @@
         <v>27</v>
       </c>
       <c r="G261" s="14">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H261" s="14" t="s">
         <v>28</v>
@@ -10018,7 +10018,7 @@
         <v>27</v>
       </c>
       <c r="G262" s="14">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H262" s="14" t="s">
         <v>28</v>
@@ -10044,7 +10044,7 @@
         <v>27</v>
       </c>
       <c r="G263" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H263" s="14" t="s">
         <v>28</v>
@@ -10070,7 +10070,7 @@
         <v>27</v>
       </c>
       <c r="G264" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H264" s="14" t="s">
         <v>28</v>
@@ -10096,7 +10096,7 @@
         <v>27</v>
       </c>
       <c r="G265" s="14">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H265" s="14" t="s">
         <v>28</v>
@@ -10122,7 +10122,7 @@
         <v>27</v>
       </c>
       <c r="G266" s="14">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="H266" s="14" t="s">
         <v>28</v>
@@ -10148,7 +10148,7 @@
         <v>27</v>
       </c>
       <c r="G267" s="14">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H267" s="14" t="s">
         <v>28</v>
@@ -10174,7 +10174,7 @@
         <v>27</v>
       </c>
       <c r="G268" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H268" s="14" t="s">
         <v>28</v>
@@ -10200,7 +10200,7 @@
         <v>27</v>
       </c>
       <c r="G269" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H269" s="14" t="s">
         <v>28</v>
@@ -10226,7 +10226,7 @@
         <v>27</v>
       </c>
       <c r="G270" s="14">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="H270" s="14" t="s">
         <v>28</v>
@@ -10252,7 +10252,7 @@
         <v>27</v>
       </c>
       <c r="G271" s="14">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="H271" s="14" t="s">
         <v>28</v>
@@ -10278,7 +10278,7 @@
         <v>27</v>
       </c>
       <c r="G272" s="14">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H272" s="14" t="s">
         <v>28</v>
@@ -10304,7 +10304,7 @@
         <v>27</v>
       </c>
       <c r="G273" s="14">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="H273" s="14" t="s">
         <v>28</v>
@@ -10330,7 +10330,7 @@
         <v>27</v>
       </c>
       <c r="G274" s="14">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H274" s="14" t="s">
         <v>28</v>
@@ -10356,7 +10356,7 @@
         <v>27</v>
       </c>
       <c r="G275" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H275" s="14" t="s">
         <v>28</v>
@@ -10382,7 +10382,7 @@
         <v>27</v>
       </c>
       <c r="G276" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H276" s="14" t="s">
         <v>28</v>
@@ -10408,7 +10408,7 @@
         <v>27</v>
       </c>
       <c r="G277" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H277" s="14" t="s">
         <v>28</v>
@@ -10434,7 +10434,7 @@
         <v>27</v>
       </c>
       <c r="G278" s="14">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H278" s="14" t="s">
         <v>28</v>
@@ -10460,7 +10460,7 @@
         <v>27</v>
       </c>
       <c r="G279" s="14">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H279" s="14" t="s">
         <v>28</v>
@@ -10486,7 +10486,7 @@
         <v>27</v>
       </c>
       <c r="G280" s="14">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="H280" s="14" t="s">
         <v>28</v>
@@ -10512,7 +10512,7 @@
         <v>27</v>
       </c>
       <c r="G281" s="14">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="H281" s="14" t="s">
         <v>28</v>
@@ -10538,7 +10538,7 @@
         <v>27</v>
       </c>
       <c r="G282" s="14">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H282" s="14" t="s">
         <v>28</v>
@@ -10564,7 +10564,7 @@
         <v>27</v>
       </c>
       <c r="G283" s="14">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H283" s="14" t="s">
         <v>28</v>
@@ -10590,7 +10590,7 @@
         <v>27</v>
       </c>
       <c r="G284" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H284" s="14" t="s">
         <v>28</v>
@@ -10616,7 +10616,7 @@
         <v>27</v>
       </c>
       <c r="G285" s="14">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H285" s="14" t="s">
         <v>28</v>
@@ -10642,7 +10642,7 @@
         <v>27</v>
       </c>
       <c r="G286" s="14">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H286" s="14" t="s">
         <v>28</v>
@@ -10668,7 +10668,7 @@
         <v>27</v>
       </c>
       <c r="G287" s="14">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="H287" s="14" t="s">
         <v>28</v>
@@ -10694,7 +10694,7 @@
         <v>27</v>
       </c>
       <c r="G288" s="14">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H288" s="14" t="s">
         <v>28</v>
@@ -10720,7 +10720,7 @@
         <v>27</v>
       </c>
       <c r="G289" s="14">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H289" s="14" t="s">
         <v>28</v>
@@ -10746,7 +10746,7 @@
         <v>27</v>
       </c>
       <c r="G290" s="14">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H290" s="14" t="s">
         <v>28</v>
@@ -10772,7 +10772,7 @@
         <v>27</v>
       </c>
       <c r="G291" s="14">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="H291" s="14" t="s">
         <v>28</v>
@@ -10798,7 +10798,7 @@
         <v>27</v>
       </c>
       <c r="G292" s="14">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H292" s="14" t="s">
         <v>28</v>
@@ -10824,7 +10824,7 @@
         <v>27</v>
       </c>
       <c r="G293" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H293" s="14" t="s">
         <v>28</v>
@@ -10850,7 +10850,7 @@
         <v>27</v>
       </c>
       <c r="G294" s="14">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H294" s="14" t="s">
         <v>28</v>
@@ -10876,7 +10876,7 @@
         <v>27</v>
       </c>
       <c r="G295" s="14">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="H295" s="14" t="s">
         <v>28</v>
@@ -10902,7 +10902,7 @@
         <v>27</v>
       </c>
       <c r="G296" s="14">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H296" s="14" t="s">
         <v>28</v>
@@ -10928,7 +10928,7 @@
         <v>27</v>
       </c>
       <c r="G297" s="14">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H297" s="14" t="s">
         <v>28</v>
@@ -10954,7 +10954,7 @@
         <v>27</v>
       </c>
       <c r="G298" s="14">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H298" s="14" t="s">
         <v>28</v>
@@ -10980,7 +10980,7 @@
         <v>27</v>
       </c>
       <c r="G299" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H299" s="14" t="s">
         <v>28</v>
@@ -11006,7 +11006,7 @@
         <v>27</v>
       </c>
       <c r="G300" s="14">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H300" s="14" t="s">
         <v>28</v>
@@ -11032,7 +11032,7 @@
         <v>27</v>
       </c>
       <c r="G301" s="14">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="H301" s="14" t="s">
         <v>28</v>
@@ -11058,7 +11058,7 @@
         <v>27</v>
       </c>
       <c r="G302" s="14">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H302" s="14" t="s">
         <v>28</v>
@@ -11084,7 +11084,7 @@
         <v>27</v>
       </c>
       <c r="G303" s="14">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H303" s="14" t="s">
         <v>28</v>
@@ -11110,7 +11110,7 @@
         <v>27</v>
       </c>
       <c r="G304" s="14">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H304" s="14" t="s">
         <v>28</v>
@@ -11136,7 +11136,7 @@
         <v>27</v>
       </c>
       <c r="G305" s="14">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H305" s="14" t="s">
         <v>28</v>
@@ -11188,7 +11188,7 @@
         <v>27</v>
       </c>
       <c r="G307" s="14">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H307" s="14" t="s">
         <v>28</v>
@@ -11214,7 +11214,7 @@
         <v>27</v>
       </c>
       <c r="G308" s="14">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H308" s="14" t="s">
         <v>28</v>
@@ -11240,7 +11240,7 @@
         <v>27</v>
       </c>
       <c r="G309" s="14">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="H309" s="14" t="s">
         <v>28</v>
@@ -11266,7 +11266,7 @@
         <v>27</v>
       </c>
       <c r="G310" s="14">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H310" s="14" t="s">
         <v>28</v>
@@ -11292,7 +11292,7 @@
         <v>27</v>
       </c>
       <c r="G311" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H311" s="14" t="s">
         <v>28</v>
@@ -11318,7 +11318,7 @@
         <v>27</v>
       </c>
       <c r="G312" s="14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H312" s="14" t="s">
         <v>28</v>
@@ -11344,7 +11344,7 @@
         <v>27</v>
       </c>
       <c r="G313" s="14">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="H313" s="14" t="s">
         <v>28</v>
@@ -11370,7 +11370,7 @@
         <v>27</v>
       </c>
       <c r="G314" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H314" s="14" t="s">
         <v>28</v>
@@ -11396,7 +11396,7 @@
         <v>27</v>
       </c>
       <c r="G315" s="14">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H315" s="14" t="s">
         <v>28</v>
@@ -11422,7 +11422,7 @@
         <v>27</v>
       </c>
       <c r="G316" s="14">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="H316" s="14" t="s">
         <v>28</v>
@@ -11448,7 +11448,7 @@
         <v>27</v>
       </c>
       <c r="G317" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H317" s="14" t="s">
         <v>28</v>
@@ -11474,7 +11474,7 @@
         <v>27</v>
       </c>
       <c r="G318" s="14">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H318" s="14" t="s">
         <v>28</v>
@@ -11500,7 +11500,7 @@
         <v>27</v>
       </c>
       <c r="G319" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H319" s="14" t="s">
         <v>28</v>
@@ -11526,7 +11526,7 @@
         <v>27</v>
       </c>
       <c r="G320" s="14">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="H320" s="14" t="s">
         <v>28</v>
@@ -11552,7 +11552,7 @@
         <v>27</v>
       </c>
       <c r="G321" s="14">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H321" s="14" t="s">
         <v>28</v>
@@ -11578,7 +11578,7 @@
         <v>27</v>
       </c>
       <c r="G322" s="14">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H322" s="14" t="s">
         <v>28</v>
@@ -11604,7 +11604,7 @@
         <v>27</v>
       </c>
       <c r="G323" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H323" s="14" t="s">
         <v>28</v>
@@ -11630,7 +11630,7 @@
         <v>27</v>
       </c>
       <c r="G324" s="14">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H324" s="14" t="s">
         <v>28</v>
@@ -11656,7 +11656,7 @@
         <v>27</v>
       </c>
       <c r="G325" s="14">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H325" s="14" t="s">
         <v>28</v>
@@ -11682,7 +11682,7 @@
         <v>27</v>
       </c>
       <c r="G326" s="14">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H326" s="14" t="s">
         <v>28</v>
@@ -11708,7 +11708,7 @@
         <v>27</v>
       </c>
       <c r="G327" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H327" s="14" t="s">
         <v>28</v>
@@ -11734,7 +11734,7 @@
         <v>27</v>
       </c>
       <c r="G328" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H328" s="14" t="s">
         <v>28</v>
@@ -11760,7 +11760,7 @@
         <v>27</v>
       </c>
       <c r="G329" s="14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H329" s="14" t="s">
         <v>28</v>
@@ -11786,7 +11786,7 @@
         <v>27</v>
       </c>
       <c r="G330" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H330" s="14" t="s">
         <v>28</v>
@@ -11812,7 +11812,7 @@
         <v>27</v>
       </c>
       <c r="G331" s="14">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H331" s="14" t="s">
         <v>28</v>
@@ -11838,7 +11838,7 @@
         <v>27</v>
       </c>
       <c r="G332" s="14">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="H332" s="14" t="s">
         <v>28</v>
@@ -11864,7 +11864,7 @@
         <v>27</v>
       </c>
       <c r="G333" s="14">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H333" s="14" t="s">
         <v>28</v>
@@ -11890,7 +11890,7 @@
         <v>27</v>
       </c>
       <c r="G334" s="14">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H334" s="14" t="s">
         <v>28</v>
@@ -11916,7 +11916,7 @@
         <v>27</v>
       </c>
       <c r="G335" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H335" s="14" t="s">
         <v>28</v>
@@ -11942,7 +11942,7 @@
         <v>27</v>
       </c>
       <c r="G336" s="14">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H336" s="14" t="s">
         <v>28</v>
@@ -11968,7 +11968,7 @@
         <v>27</v>
       </c>
       <c r="G337" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H337" s="14" t="s">
         <v>28</v>
@@ -11994,7 +11994,7 @@
         <v>27</v>
       </c>
       <c r="G338" s="14">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="H338" s="14" t="s">
         <v>28</v>
@@ -12020,7 +12020,7 @@
         <v>27</v>
       </c>
       <c r="G339" s="14">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="H339" s="14" t="s">
         <v>28</v>
@@ -12046,7 +12046,7 @@
         <v>27</v>
       </c>
       <c r="G340" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H340" s="14" t="s">
         <v>28</v>
@@ -12072,7 +12072,7 @@
         <v>27</v>
       </c>
       <c r="G341" s="14">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H341" s="14" t="s">
         <v>28</v>
@@ -12098,7 +12098,7 @@
         <v>27</v>
       </c>
       <c r="G342" s="14">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H342" s="14" t="s">
         <v>28</v>
@@ -12124,7 +12124,7 @@
         <v>27</v>
       </c>
       <c r="G343" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H343" s="14" t="s">
         <v>28</v>
@@ -12150,7 +12150,7 @@
         <v>27</v>
       </c>
       <c r="G344" s="14">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H344" s="14" t="s">
         <v>28</v>
@@ -12176,7 +12176,7 @@
         <v>27</v>
       </c>
       <c r="G345" s="14">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H345" s="14" t="s">
         <v>28</v>
@@ -12202,7 +12202,7 @@
         <v>27</v>
       </c>
       <c r="G346" s="14">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H346" s="14" t="s">
         <v>28</v>
@@ -12228,7 +12228,7 @@
         <v>27</v>
       </c>
       <c r="G347" s="14">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H347" s="14" t="s">
         <v>28</v>
@@ -12254,7 +12254,7 @@
         <v>27</v>
       </c>
       <c r="G348" s="14">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H348" s="14" t="s">
         <v>28</v>
@@ -12280,7 +12280,7 @@
         <v>27</v>
       </c>
       <c r="G349" s="14">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H349" s="14" t="s">
         <v>28</v>
@@ -12306,7 +12306,7 @@
         <v>27</v>
       </c>
       <c r="G350" s="14">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H350" s="14" t="s">
         <v>28</v>
@@ -12332,7 +12332,7 @@
         <v>27</v>
       </c>
       <c r="G351" s="14">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="H351" s="14" t="s">
         <v>28</v>
@@ -12358,7 +12358,7 @@
         <v>27</v>
       </c>
       <c r="G352" s="14">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H352" s="14" t="s">
         <v>28</v>
@@ -12384,7 +12384,7 @@
         <v>27</v>
       </c>
       <c r="G353" s="14">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H353" s="14" t="s">
         <v>28</v>
@@ -12410,7 +12410,7 @@
         <v>27</v>
       </c>
       <c r="G354" s="14">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H354" s="14" t="s">
         <v>28</v>
@@ -12436,7 +12436,7 @@
         <v>27</v>
       </c>
       <c r="G355" s="14">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H355" s="14" t="s">
         <v>28</v>
@@ -12462,7 +12462,7 @@
         <v>27</v>
       </c>
       <c r="G356" s="14">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H356" s="14" t="s">
         <v>28</v>
@@ -12488,7 +12488,7 @@
         <v>27</v>
       </c>
       <c r="G357" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H357" s="14" t="s">
         <v>28</v>
@@ -12514,7 +12514,7 @@
         <v>27</v>
       </c>
       <c r="G358" s="14">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="H358" s="14" t="s">
         <v>28</v>
@@ -12540,7 +12540,7 @@
         <v>27</v>
       </c>
       <c r="G359" s="14">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H359" s="14" t="s">
         <v>28</v>
@@ -12566,7 +12566,7 @@
         <v>27</v>
       </c>
       <c r="G360" s="14">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H360" s="14" t="s">
         <v>28</v>
@@ -12592,7 +12592,7 @@
         <v>27</v>
       </c>
       <c r="G361" s="14">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="H361" s="14" t="s">
         <v>28</v>
@@ -12618,7 +12618,7 @@
         <v>27</v>
       </c>
       <c r="G362" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H362" s="14" t="s">
         <v>28</v>
@@ -12644,7 +12644,7 @@
         <v>27</v>
       </c>
       <c r="G363" s="14">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H363" s="14" t="s">
         <v>28</v>
@@ -12670,7 +12670,7 @@
         <v>27</v>
       </c>
       <c r="G364" s="14">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H364" s="14" t="s">
         <v>28</v>
@@ -12696,7 +12696,7 @@
         <v>27</v>
       </c>
       <c r="G365" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H365" s="14" t="s">
         <v>28</v>
@@ -12722,7 +12722,7 @@
         <v>27</v>
       </c>
       <c r="G366" s="14">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="H366" s="14" t="s">
         <v>28</v>
@@ -12748,7 +12748,7 @@
         <v>27</v>
       </c>
       <c r="G367" s="14">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H367" s="14" t="s">
         <v>28</v>
@@ -12774,7 +12774,7 @@
         <v>27</v>
       </c>
       <c r="G368" s="14">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H368" s="14" t="s">
         <v>28</v>
@@ -12800,7 +12800,7 @@
         <v>27</v>
       </c>
       <c r="G369" s="14">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="H369" s="14" t="s">
         <v>28</v>
@@ -12826,7 +12826,7 @@
         <v>27</v>
       </c>
       <c r="G370" s="14">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H370" s="14" t="s">
         <v>28</v>
@@ -12852,7 +12852,7 @@
         <v>27</v>
       </c>
       <c r="G371" s="14">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H371" s="14" t="s">
         <v>28</v>
@@ -12878,7 +12878,7 @@
         <v>27</v>
       </c>
       <c r="G372" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H372" s="14" t="s">
         <v>28</v>
@@ -12904,7 +12904,7 @@
         <v>27</v>
       </c>
       <c r="G373" s="14">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H373" s="14" t="s">
         <v>28</v>
@@ -12930,7 +12930,7 @@
         <v>27</v>
       </c>
       <c r="G374" s="14">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H374" s="14" t="s">
         <v>28</v>
@@ -12956,7 +12956,7 @@
         <v>27</v>
       </c>
       <c r="G375" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H375" s="14" t="s">
         <v>28</v>
@@ -12982,7 +12982,7 @@
         <v>27</v>
       </c>
       <c r="G376" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H376" s="14" t="s">
         <v>28</v>
@@ -13008,7 +13008,7 @@
         <v>27</v>
       </c>
       <c r="G377" s="14">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H377" s="14" t="s">
         <v>28</v>
@@ -13034,7 +13034,7 @@
         <v>27</v>
       </c>
       <c r="G378" s="14">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H378" s="14" t="s">
         <v>28</v>
@@ -13060,7 +13060,7 @@
         <v>27</v>
       </c>
       <c r="G379" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H379" s="14" t="s">
         <v>28</v>
@@ -13086,7 +13086,7 @@
         <v>27</v>
       </c>
       <c r="G380" s="14">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="H380" s="14" t="s">
         <v>28</v>
@@ -13112,7 +13112,7 @@
         <v>27</v>
       </c>
       <c r="G381" s="14">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="H381" s="14" t="s">
         <v>28</v>
@@ -13138,7 +13138,7 @@
         <v>27</v>
       </c>
       <c r="G382" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H382" s="14" t="s">
         <v>28</v>
@@ -13164,7 +13164,7 @@
         <v>27</v>
       </c>
       <c r="G383" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H383" s="14" t="s">
         <v>28</v>
@@ -13190,7 +13190,7 @@
         <v>27</v>
       </c>
       <c r="G384" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H384" s="14" t="s">
         <v>28</v>
@@ -13216,7 +13216,7 @@
         <v>27</v>
       </c>
       <c r="G385" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H385" s="14" t="s">
         <v>28</v>
@@ -13242,7 +13242,7 @@
         <v>27</v>
       </c>
       <c r="G386" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H386" s="14" t="s">
         <v>28</v>
@@ -13268,7 +13268,7 @@
         <v>27</v>
       </c>
       <c r="G387" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H387" s="14" t="s">
         <v>28</v>
@@ -13294,7 +13294,7 @@
         <v>27</v>
       </c>
       <c r="G388" s="14">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H388" s="14" t="s">
         <v>28</v>
@@ -13320,7 +13320,7 @@
         <v>27</v>
       </c>
       <c r="G389" s="14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H389" s="14" t="s">
         <v>28</v>
@@ -13346,7 +13346,7 @@
         <v>27</v>
       </c>
       <c r="G390" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H390" s="14" t="s">
         <v>28</v>
@@ -13372,7 +13372,7 @@
         <v>27</v>
       </c>
       <c r="G391" s="14">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H391" s="14" t="s">
         <v>28</v>
@@ -13398,7 +13398,7 @@
         <v>27</v>
       </c>
       <c r="G392" s="14">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H392" s="14" t="s">
         <v>28</v>
@@ -13424,7 +13424,7 @@
         <v>27</v>
       </c>
       <c r="G393" s="14">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H393" s="14" t="s">
         <v>28</v>
@@ -13450,7 +13450,7 @@
         <v>27</v>
       </c>
       <c r="G394" s="14">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H394" s="14" t="s">
         <v>28</v>
@@ -13476,7 +13476,7 @@
         <v>27</v>
       </c>
       <c r="G395" s="14">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="H395" s="14" t="s">
         <v>28</v>
@@ -13502,7 +13502,7 @@
         <v>27</v>
       </c>
       <c r="G396" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H396" s="14" t="s">
         <v>28</v>
@@ -13528,7 +13528,7 @@
         <v>27</v>
       </c>
       <c r="G397" s="14">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H397" s="14" t="s">
         <v>28</v>
@@ -13554,7 +13554,7 @@
         <v>27</v>
       </c>
       <c r="G398" s="14">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H398" s="14" t="s">
         <v>28</v>
@@ -13580,7 +13580,7 @@
         <v>27</v>
       </c>
       <c r="G399" s="14">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H399" s="14" t="s">
         <v>28</v>
@@ -13606,7 +13606,7 @@
         <v>27</v>
       </c>
       <c r="G400" s="14">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H400" s="14" t="s">
         <v>28</v>
@@ -13632,7 +13632,7 @@
         <v>27</v>
       </c>
       <c r="G401" s="14">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H401" s="14" t="s">
         <v>28</v>
